--- a/tiflow-diga/develop/0.9.0/StructureDefinition-GEM-ERP-EX-DeepLink.xlsx
+++ b/tiflow-diga/develop/0.9.0/StructureDefinition-GEM-ERP-EX-DeepLink.xlsx
@@ -1317,7 +1317,7 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>107</v>
